--- a/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACF5F29C-D0BC-4E91-A004-D1ABCD0CB8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3B7C50F-1200-43C7-B1E9-F08879A34A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,13 +621,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH04,S01aH03,S02aH03,S03aH02,S03aH05,S02aH04,S02aH05,S02aH02,S01aH05,S04aH05,S01aH04,S04aH03,S03aH03,S04aH02,S01aH02,S04aH04</t>
+    <t>S01aH03,S03aH04,S04aH03,S04aH02,S01aH04,S03aH02,S04aH05,S02aH02,S01aH05,S01aH02,S04aH04,S03aH05,S02aH04,S02aH05,S02aH03,S03aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S04aH06,S02aH06,S03aH01,S01aH06,S02aH01,S03aH06</t>
+    <t>S02aH01,S03aH01,S03aH06,S02aH06,S01aH06,S01aH01,S04aH01,S04aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH01,S04aH01,S04aH06,S02aH06,S03aH01,S01aH06,S02aH01,S03aH06</v>
+        <v>S02aH01,S03aH01,S03aH06,S02aH06,S01aH06,S01aH01,S04aH01,S04aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH04,S01aH03,S02aH03,S03aH02,S03aH05,S02aH04,S02aH05,S02aH02,S01aH05,S04aH05,S01aH04,S04aH03,S03aH03,S04aH02,S01aH02,S04aH04</v>
+        <v>S01aH03,S03aH04,S04aH03,S04aH02,S01aH04,S03aH02,S04aH05,S02aH02,S01aH05,S01aH02,S04aH04,S03aH05,S02aH04,S02aH05,S02aH03,S03aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1350,7 +1350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E95E65-5284-48A0-8CE8-7BB5CED8EECE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A4E0AC-B0A5-47A5-8C86-419F4F9E561D}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1456,7 +1456,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE1FCBA-C36D-4106-B8AA-2B74BA8F2AE8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B07BA5C-35BB-40D8-8B8B-F607B35A559D}">
   <dimension ref="B9:O490"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16878,7 +16878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D5453FD-760B-4E6C-A548-9C9C92E06889}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47AC662D-2C0A-4A6A-944C-362B3987F998}">
   <dimension ref="B9:DH60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26051,7 +26051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB51CF1D-3806-4862-9C14-79883490DBC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD2C5117-616E-4543-84B4-85A81E7BCAAB}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26417,7 +26417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47037ECF-BD08-4148-938F-1FB780BDF4AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D404CE-2EEA-494A-B43E-52C7E6231032}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26972,7 +26972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE7B3EB4-75A5-4345-B4D4-37EF56734577}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25057881-5A0B-45F3-8773-B315441E1042}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27263,7 +27263,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB9FD95-B8E2-4F88-A204-9FB3A2F5C55C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51897CD0-3B37-4950-86B2-6E4C308CBBB2}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27351,7 +27351,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="E15" t="s">
         <v>201</v>
@@ -27799,7 +27799,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.30260000000000004</v>
+        <v>0.30259999999999998</v>
       </c>
       <c r="E47" t="s">
         <v>201</v>
@@ -27967,7 +27967,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.29859999999999998</v>
+        <v>0.29860000000000003</v>
       </c>
       <c r="E59" t="s">
         <v>201</v>
@@ -28079,7 +28079,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.37279999999999996</v>
+        <v>0.37280000000000002</v>
       </c>
       <c r="E67" t="s">
         <v>201</v>
@@ -28247,7 +28247,7 @@
         <v>37</v>
       </c>
       <c r="D79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="E79" t="s">
         <v>201</v>
@@ -28303,7 +28303,7 @@
         <v>37</v>
       </c>
       <c r="D83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="E83" t="s">
         <v>201</v>
@@ -28415,7 +28415,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="E91" t="s">
         <v>201</v>
@@ -28695,7 +28695,7 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="E111" t="s">
         <v>201</v>
@@ -28807,7 +28807,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.31936666666666669</v>
+        <v>0.31936666666666663</v>
       </c>
       <c r="E119" t="s">
         <v>201</v>
